--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
@@ -935,43 +935,43 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 4.938,57</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>5.41</t>
-  </si>
-  <si>
-    <t>18.6</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.893,99</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>5.43</t>
+  </si>
+  <si>
+    <t>18.7</t>
   </si>
   <si>
     <t>6.6</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>40.8%</t>
+  </si>
+  <si>
+    <t>16.3%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>3.9%</t>
+    <t>3.8%</t>
   </si>
   <si>
     <t>1.2%</t>
@@ -980,40 +980,40 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>6.5%</t>
+    <t>6.4%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>1110.0</t>
-  </si>
-  <si>
-    <t>894.0</t>
-  </si>
-  <si>
-    <t>99.0</t>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>1127.0</t>
+  </si>
+  <si>
+    <t>905.0</t>
+  </si>
+  <si>
+    <t>103.0</t>
   </si>
   <si>
     <t>28.0</t>
   </si>
   <si>
-    <t>211.0</t>
-  </si>
-  <si>
-    <t>67.0</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>350.0</t>
-  </si>
-  <si>
-    <t>145.0</t>
+    <t>213.0</t>
+  </si>
+  <si>
+    <t>69.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>353.0</t>
+  </si>
+  <si>
+    <t>148.0</t>
   </si>
   <si>
     <t>188.0</t>
@@ -1022,7 +1022,7 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>36.0</t>
+    <t>38.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6785,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>43</v>
+      </c>
+      <c r="O36" s="6">
+        <v>25</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.7746204545454551</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>25.765331999999997</v>
+      </c>
+      <c r="R36" s="8">
+        <v>12.218054166666667</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7667,7 +7725,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7697,35 +7755,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>51</v>
+      </c>
+      <c r="O42" s="6">
+        <v>32</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.2634744680851071</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.276562500000001</v>
+      </c>
+      <c r="R42" s="8">
+        <v>7.1338531249999999</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9016,7 +9132,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9046,35 +9162,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
+      <c r="O51" s="6">
+        <v>5</v>
+      </c>
+      <c r="P51" s="7">
+        <v>3.9799999999999995</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>18.953340000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>8.8133400000000002</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -10085,33 +10259,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>50</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16573,7 +16793,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16603,35 +16823,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="N102" s="6">
+        <v>23</v>
+      </c>
+      <c r="O102" s="6">
+        <v>18</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.6388875000000001</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>21.79815</v>
+      </c>
+      <c r="R102" s="8">
+        <v>8.9813705882352934</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -30382,7 +30660,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30412,14 +30690,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="N195" s="6">
+        <v>51</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>6.3996369565217393</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>22.025521874999999</v>
+      </c>
+      <c r="R195" s="8">
+        <v>8.0656250000000007</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.15625</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 4.893,99</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>5.43</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 4.901,63</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>5.44</t>
   </si>
   <si>
     <t>18.7</t>
@@ -956,16 +956,16 @@
     <t>6.6</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>40.8%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>40.9%</t>
+  </si>
+  <si>
+    <t>16.2%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -980,28 +980,28 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
   </si>
   <si>
     <t>3.4%</t>
   </si>
   <si>
-    <t>1127.0</t>
-  </si>
-  <si>
-    <t>905.0</t>
-  </si>
-  <si>
-    <t>103.0</t>
+    <t>1136.0</t>
+  </si>
+  <si>
+    <t>914.0</t>
+  </si>
+  <si>
+    <t>104.0</t>
   </si>
   <si>
     <t>28.0</t>
   </si>
   <si>
-    <t>213.0</t>
+    <t>215.0</t>
   </si>
   <si>
     <t>69.0</t>
@@ -1010,13 +1010,13 @@
     <t>15.0</t>
   </si>
   <si>
-    <t>353.0</t>
-  </si>
-  <si>
-    <t>148.0</t>
-  </si>
-  <si>
-    <t>188.0</t>
+    <t>356.0</t>
+  </si>
+  <si>
+    <t>149.0</t>
+  </si>
+  <si>
+    <t>190.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>8444.5599999999995</v>
+      </c>
+      <c r="N6" s="6">
+        <v>79</v>
+      </c>
+      <c r="O6" s="6">
+        <v>55</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.5162443037974684</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>13.620605454545453</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.4966055555555555</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -7146,7 +7204,7 @@
         <v>6.8833315789473684</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.2857142857142857</v>
@@ -25093,7 +25151,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25123,35 +25181,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2779.5999999999999</v>
+      </c>
+      <c r="N158" s="6">
+        <v>27</v>
+      </c>
+      <c r="O158" s="6">
+        <v>21</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.4398821428571429</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>19.597619047619048</v>
+      </c>
+      <c r="R158" s="8">
+        <v>5.6880952380952383</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30696,7 +30812,9 @@
       <c r="N195" s="6">
         <v>51</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>32</v>
+      </c>
       <c r="P195" s="7">
         <v>6.3996369565217393</v>
       </c>
@@ -30706,31 +30824,75 @@
       <c r="R195" s="8">
         <v>8.0656250000000007</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.15625</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
@@ -932,34 +932,37 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>R$ 4.901,63</t>
+    <t>R$ 4.885,78</t>
   </si>
   <si>
-    <t>51.6</t>
+    <t>51.4</t>
   </si>
   <si>
-    <t>30.2</t>
+    <t>30.1</t>
   </si>
   <si>
-    <t>5.44</t>
+    <t>5.43</t>
   </si>
   <si>
-    <t>18.7</t>
+    <t>18.6</t>
   </si>
   <si>
     <t>6.6</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>40.9%</t>
+    <t>40.6%</t>
   </si>
   <si>
     <t>16.2%</t>
@@ -983,19 +986,19 @@
     <t>6.3%</t>
   </si>
   <si>
-    <t>2.6%</t>
+    <t>2.7%</t>
   </si>
   <si>
-    <t>3.4%</t>
+    <t>3.3%</t>
   </si>
   <si>
-    <t>1136.0</t>
+    <t>1147.0</t>
   </si>
   <si>
-    <t>914.0</t>
+    <t>924.0</t>
   </si>
   <si>
-    <t>104.0</t>
+    <t>105.0</t>
   </si>
   <si>
     <t>28.0</t>
@@ -1004,16 +1007,16 @@
     <t>215.0</t>
   </si>
   <si>
-    <t>69.0</t>
+    <t>70.0</t>
   </si>
   <si>
-    <t>15.0</t>
+    <t>16.0</t>
   </si>
   <si>
-    <t>356.0</t>
+    <t>359.0</t>
   </si>
   <si>
-    <t>149.0</t>
+    <t>154.0</t>
   </si>
   <si>
     <t>190.0</t>
@@ -18897,33 +18900,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>12</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22664,7 +22713,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22694,35 +22743,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>1905.4100000000001</v>
+      </c>
+      <c r="N141" s="6">
+        <v>25</v>
+      </c>
+      <c r="O141" s="6">
+        <v>13</v>
+      </c>
+      <c r="P141" s="7">
+        <v>4.9104166666666664</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>13.453846153846154</v>
+      </c>
+      <c r="R141" s="8">
+        <v>2.2111083333333332</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33551,137 +33658,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>41</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Z217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AA217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>336</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>337</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>338</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>338</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>339</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>339</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>